--- a/output/【PO2603230466】出口合同.xlsx
+++ b/output/【PO2603230466】出口合同.xlsx
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>16</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>40</v>
+        <v>36.67</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>9830.09</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>55.85</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>7408.57</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>123.48</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>73.33</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>3704.28</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>102.9</v>
+        <v>123.48</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1">
